--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/89.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/89.xlsx
@@ -426,13 +426,13 @@
         <v>-11.73643717756402</v>
       </c>
       <c r="E2">
-        <v>-7.078219788974732</v>
+        <v>-4.537927009631967</v>
       </c>
       <c r="F2">
-        <v>-5.168824701315987</v>
+        <v>-5.099601350933644</v>
       </c>
       <c r="G2">
-        <v>-7.42653802727877</v>
+        <v>-6.475338840753215</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.85018875873365</v>
       </c>
       <c r="E3">
-        <v>-7.724093394318716</v>
+        <v>-5.435869063664907</v>
       </c>
       <c r="F3">
-        <v>-5.162930867245069</v>
+        <v>-5.319199892680987</v>
       </c>
       <c r="G3">
-        <v>-6.910162444608789</v>
+        <v>-6.356536603530929</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.98458919908463</v>
       </c>
       <c r="E4">
-        <v>-7.28911082351194</v>
+        <v>-5.855803515344195</v>
       </c>
       <c r="F4">
-        <v>-5.418504576928592</v>
+        <v>-5.265277316595753</v>
       </c>
       <c r="G4">
-        <v>-6.707179655413916</v>
+        <v>-6.641826175923163</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.10375031086195</v>
       </c>
       <c r="E5">
-        <v>-8.612833589168069</v>
+        <v>-6.68550599455555</v>
       </c>
       <c r="F5">
-        <v>-5.416431173319385</v>
+        <v>-5.448796316114164</v>
       </c>
       <c r="G5">
-        <v>-6.876974225577596</v>
+        <v>-6.706020964475171</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.19364105379189</v>
       </c>
       <c r="E6">
-        <v>-10.26052338533294</v>
+        <v>-7.697556536633767</v>
       </c>
       <c r="F6">
-        <v>-5.18445765094162</v>
+        <v>-5.099225272132773</v>
       </c>
       <c r="G6">
-        <v>-6.842004933046274</v>
+        <v>-6.350534584468231</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.2338835167218</v>
       </c>
       <c r="E7">
-        <v>-10.38665950034259</v>
+        <v>-8.979232421128678</v>
       </c>
       <c r="F7">
-        <v>-5.466230964840886</v>
+        <v>-5.30457755128677</v>
       </c>
       <c r="G7">
-        <v>-6.601268682521552</v>
+        <v>-6.461321990939942</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.20418748813276</v>
       </c>
       <c r="E8">
-        <v>-11.52963275445656</v>
+        <v>-9.703217674630968</v>
       </c>
       <c r="F8">
-        <v>-5.359367428042735</v>
+        <v>-4.925520769602731</v>
       </c>
       <c r="G8">
-        <v>-6.97516500627238</v>
+        <v>-6.564409068487307</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.09251722538571</v>
       </c>
       <c r="E9">
-        <v>-12.71174108094482</v>
+        <v>-9.504490121278362</v>
       </c>
       <c r="F9">
-        <v>-5.182306380796549</v>
+        <v>-4.796939096237983</v>
       </c>
       <c r="G9">
-        <v>-6.631454236748627</v>
+        <v>-5.915399789331966</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.88877012151058</v>
       </c>
       <c r="E10">
-        <v>-12.43553586579499</v>
+        <v>-10.64110086941156</v>
       </c>
       <c r="F10">
-        <v>-4.996362749890144</v>
+        <v>-5.128933840666774</v>
       </c>
       <c r="G10">
-        <v>-6.665562787439738</v>
+        <v>-5.601775257669109</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.59002921536735</v>
       </c>
       <c r="E11">
-        <v>-13.06240346572878</v>
+        <v>-11.70937694476901</v>
       </c>
       <c r="F11">
-        <v>-4.936736035869233</v>
+        <v>-4.678282092726176</v>
       </c>
       <c r="G11">
-        <v>-6.053426364500799</v>
+        <v>-5.586636132918023</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.2033995372157</v>
       </c>
       <c r="E12">
-        <v>-14.34516165551152</v>
+        <v>-12.60081611012694</v>
       </c>
       <c r="F12">
-        <v>-4.766201695389705</v>
+        <v>-4.809458212796492</v>
       </c>
       <c r="G12">
-        <v>-5.546287203885385</v>
+        <v>-5.308643002894343</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.73626279109199</v>
       </c>
       <c r="E13">
-        <v>-14.30523410018589</v>
+        <v>-13.94965379262961</v>
       </c>
       <c r="F13">
-        <v>-4.573390070346688</v>
+        <v>-4.407603931820007</v>
       </c>
       <c r="G13">
-        <v>-5.228365584112555</v>
+        <v>-4.795846119952314</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.21226639123422</v>
       </c>
       <c r="E14">
-        <v>-15.39826734294328</v>
+        <v>-14.04822055788056</v>
       </c>
       <c r="F14">
-        <v>-4.367263267671074</v>
+        <v>-4.203226641099104</v>
       </c>
       <c r="G14">
-        <v>-5.347568397345093</v>
+        <v>-3.854896382416343</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.651002905428102</v>
       </c>
       <c r="E15">
-        <v>-17.21748214909668</v>
+        <v>-16.09738221719545</v>
       </c>
       <c r="F15">
-        <v>-4.314602295140303</v>
+        <v>-4.333517236415828</v>
       </c>
       <c r="G15">
-        <v>-4.945092133953738</v>
+        <v>-4.192191314684988</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.079636144679247</v>
       </c>
       <c r="E16">
-        <v>-17.1801267670074</v>
+        <v>-17.01541258192641</v>
       </c>
       <c r="F16">
-        <v>-3.888131420054826</v>
+        <v>-3.891322291290409</v>
       </c>
       <c r="G16">
-        <v>-4.518753458315316</v>
+        <v>-3.041336437231527</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.524642726091923</v>
       </c>
       <c r="E17">
-        <v>-18.93712034029541</v>
+        <v>-17.33065777149637</v>
       </c>
       <c r="F17">
-        <v>-3.81853447597382</v>
+        <v>-3.63517866483376</v>
       </c>
       <c r="G17">
-        <v>-3.339596727046626</v>
+        <v>-2.834745153398848</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.012940721467432</v>
       </c>
       <c r="E18">
-        <v>-18.9925533906233</v>
+        <v>-18.32646920578308</v>
       </c>
       <c r="F18">
-        <v>-3.18315348373932</v>
+        <v>-3.429891826704584</v>
       </c>
       <c r="G18">
-        <v>-3.945403386914478</v>
+        <v>-2.207688101714414</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.57564981234174</v>
       </c>
       <c r="E19">
-        <v>-20.21209861173298</v>
+        <v>-19.95262610804148</v>
       </c>
       <c r="F19">
-        <v>-3.237572251898831</v>
+        <v>-3.111731646269947</v>
       </c>
       <c r="G19">
-        <v>-2.78527236085998</v>
+        <v>-1.862884852162702</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.233186113041565</v>
       </c>
       <c r="E20">
-        <v>-20.74694761983091</v>
+        <v>-19.86676171238204</v>
       </c>
       <c r="F20">
-        <v>-3.018880772457553</v>
+        <v>-2.769910807709148</v>
       </c>
       <c r="G20">
-        <v>-3.22733612780994</v>
+        <v>-2.332687680186216</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.006573153568261</v>
       </c>
       <c r="E21">
-        <v>-21.31272610540123</v>
+        <v>-21.33900031159373</v>
       </c>
       <c r="F21">
-        <v>-2.710694963920025</v>
+        <v>-2.650276330662038</v>
       </c>
       <c r="G21">
-        <v>-3.055194380858917</v>
+        <v>-2.124775488683367</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.90120527738094</v>
       </c>
       <c r="E22">
-        <v>-23.29391084138697</v>
+        <v>-21.43244990121601</v>
       </c>
       <c r="F22">
-        <v>-2.631194059171148</v>
+        <v>-2.359550021873315</v>
       </c>
       <c r="G22">
-        <v>-3.458398964268911</v>
+        <v>-1.420847569577056</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.912879031508593</v>
       </c>
       <c r="E23">
-        <v>-22.99343753403003</v>
+        <v>-22.5700569136309</v>
       </c>
       <c r="F23">
-        <v>-2.635917410101911</v>
+        <v>-2.236332027441694</v>
       </c>
       <c r="G23">
-        <v>-3.105951665067022</v>
+        <v>-2.09623527558931</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.026399414692611</v>
       </c>
       <c r="E24">
-        <v>-24.17377069870728</v>
+        <v>-23.75351019689944</v>
       </c>
       <c r="F24">
-        <v>-2.338239442068895</v>
+        <v>-1.97769253000041</v>
       </c>
       <c r="G24">
-        <v>-2.779919208722978</v>
+        <v>-1.638552354785069</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.21262724888192</v>
       </c>
       <c r="E25">
-        <v>-23.26055863032048</v>
+        <v>-23.95907121752962</v>
       </c>
       <c r="F25">
-        <v>-2.326533782299935</v>
+        <v>-2.022983517748473</v>
       </c>
       <c r="G25">
-        <v>-3.482201786696271</v>
+        <v>-2.167299446135305</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.443679075650009</v>
       </c>
       <c r="E26">
-        <v>-25.03203426348501</v>
+        <v>-24.14522772703694</v>
       </c>
       <c r="F26">
-        <v>-1.787641853510925</v>
+        <v>-1.566184455311699</v>
       </c>
       <c r="G26">
-        <v>-3.822479520495799</v>
+        <v>-1.900555549854069</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.681866052332937</v>
       </c>
       <c r="E27">
-        <v>-25.43212494206269</v>
+        <v>-23.90458461826933</v>
       </c>
       <c r="F27">
-        <v>-2.05865301811302</v>
+        <v>-1.930364586808863</v>
       </c>
       <c r="G27">
-        <v>-4.649798092941826</v>
+        <v>-2.334435648230951</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.89269303542103</v>
       </c>
       <c r="E28">
-        <v>-24.15909391444842</v>
+        <v>-23.80935533836203</v>
       </c>
       <c r="F28">
-        <v>-2.159916791268245</v>
+        <v>-1.931434009125877</v>
       </c>
       <c r="G28">
-        <v>-4.116065320009447</v>
+        <v>-2.247209394362233</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.042198938448315</v>
       </c>
       <c r="E29">
-        <v>-24.40292054044342</v>
+        <v>-23.90712962066164</v>
       </c>
       <c r="F29">
-        <v>-2.160501618654621</v>
+        <v>-2.019246752394444</v>
       </c>
       <c r="G29">
-        <v>-4.211117703533001</v>
+        <v>-3.10001254636957</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.103655271501987</v>
       </c>
       <c r="E30">
-        <v>-23.55219235641445</v>
+        <v>-23.74861491649715</v>
       </c>
       <c r="F30">
-        <v>-2.223218143087975</v>
+        <v>-1.865431351205618</v>
       </c>
       <c r="G30">
-        <v>-3.708662964855656</v>
+        <v>-2.898168584840206</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.063621394747759</v>
       </c>
       <c r="E31">
-        <v>-24.07191173285275</v>
+        <v>-23.65758806046897</v>
       </c>
       <c r="F31">
-        <v>-2.458472000380826</v>
+        <v>-2.157877350722553</v>
       </c>
       <c r="G31">
-        <v>-4.438161537707297</v>
+        <v>-2.69614916439726</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.915538846492335</v>
       </c>
       <c r="E32">
-        <v>-24.22662704732481</v>
+        <v>-23.75462872997934</v>
       </c>
       <c r="F32">
-        <v>-2.397309493195125</v>
+        <v>-2.124521480514025</v>
       </c>
       <c r="G32">
-        <v>-4.162263983009976</v>
+        <v>-2.691127066814186</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.665889343856886</v>
       </c>
       <c r="E33">
-        <v>-22.79584662765334</v>
+        <v>-23.8576288712838</v>
       </c>
       <c r="F33">
-        <v>-2.260692656023222</v>
+        <v>-2.137337152602736</v>
       </c>
       <c r="G33">
-        <v>-4.363025396147999</v>
+        <v>-2.859564313306764</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.32671396869902</v>
       </c>
       <c r="E34">
-        <v>-23.18493311439238</v>
+        <v>-22.56050636194873</v>
       </c>
       <c r="F34">
-        <v>-2.261087787274357</v>
+        <v>-2.325612637748022</v>
       </c>
       <c r="G34">
-        <v>-4.222850276924178</v>
+        <v>-2.312920412771228</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.918762893268967</v>
       </c>
       <c r="E35">
-        <v>-22.88733991650432</v>
+        <v>-22.6822272148009</v>
       </c>
       <c r="F35">
-        <v>-2.560723187480189</v>
+        <v>-2.314334415558907</v>
       </c>
       <c r="G35">
-        <v>-3.900207819212348</v>
+        <v>-2.969808790310034</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.470220596989325</v>
       </c>
       <c r="E36">
-        <v>-21.2367881247666</v>
+        <v>-21.89625620908161</v>
       </c>
       <c r="F36">
-        <v>-2.540272453039874</v>
+        <v>-2.258422929339551</v>
       </c>
       <c r="G36">
-        <v>-4.395283351882657</v>
+        <v>-1.959486570998635</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.007947162821138</v>
       </c>
       <c r="E37">
-        <v>-21.92637056123262</v>
+        <v>-21.69577160781403</v>
       </c>
       <c r="F37">
-        <v>-2.369116008640844</v>
+        <v>-2.40465214185354</v>
       </c>
       <c r="G37">
-        <v>-3.92259041760336</v>
+        <v>-2.554613410956799</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.564002412162026</v>
       </c>
       <c r="E38">
-        <v>-20.59513958567177</v>
+        <v>-21.27251325621311</v>
       </c>
       <c r="F38">
-        <v>-2.539597333606593</v>
+        <v>-2.430812812801351</v>
       </c>
       <c r="G38">
-        <v>-3.585854967530852</v>
+        <v>-1.875603968124582</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.162794004475475</v>
       </c>
       <c r="E39">
-        <v>-21.55125894528125</v>
+        <v>-20.7670178166329</v>
       </c>
       <c r="F39">
-        <v>-2.33322864764936</v>
+        <v>-2.633836551186079</v>
       </c>
       <c r="G39">
-        <v>-3.31709163847066</v>
+        <v>-1.761121992831045</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.827665959943245</v>
       </c>
       <c r="E40">
-        <v>-21.1587398752444</v>
+        <v>-20.20373904871482</v>
       </c>
       <c r="F40">
-        <v>-2.554956093621898</v>
+        <v>-2.834904514132797</v>
       </c>
       <c r="G40">
-        <v>-2.392356952986039</v>
+        <v>-1.778472562002365</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.574916029850783</v>
       </c>
       <c r="E41">
-        <v>-19.71892062145363</v>
+        <v>-18.82749504151773</v>
       </c>
       <c r="F41">
-        <v>-2.43669504972863</v>
+        <v>-2.629092491070246</v>
       </c>
       <c r="G41">
-        <v>-2.402675923431948</v>
+        <v>-1.066192136500473</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.413349719216613</v>
       </c>
       <c r="E42">
-        <v>-19.47433321182535</v>
+        <v>-18.54907993105214</v>
       </c>
       <c r="F42">
-        <v>-2.262080999790314</v>
+        <v>-2.808920285441782</v>
       </c>
       <c r="G42">
-        <v>-2.148416094379303</v>
+        <v>-1.010929199813419</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.347836152083336</v>
       </c>
       <c r="E43">
-        <v>-18.15052893363708</v>
+        <v>-18.90698334577436</v>
       </c>
       <c r="F43">
-        <v>-2.890285016846958</v>
+        <v>-2.706303788317785</v>
       </c>
       <c r="G43">
-        <v>-2.430696380876339</v>
+        <v>-1.057511886096504</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.371200336614131</v>
       </c>
       <c r="E44">
-        <v>-18.41234718686455</v>
+        <v>-16.99445933269292</v>
       </c>
       <c r="F44">
-        <v>-2.91253413691875</v>
+        <v>-2.780479119034064</v>
       </c>
       <c r="G44">
-        <v>-2.179846413729143</v>
+        <v>-0.4430845656443896</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.475059010398956</v>
       </c>
       <c r="E45">
-        <v>-17.97150024221784</v>
+        <v>-17.19847614368648</v>
       </c>
       <c r="F45">
-        <v>-3.045592307728226</v>
+        <v>-2.98844075550688</v>
       </c>
       <c r="G45">
-        <v>-1.793237595107515</v>
+        <v>-0.4487886356085539</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.64225040639052</v>
       </c>
       <c r="E46">
-        <v>-18.1709704653077</v>
+        <v>-15.86876673539221</v>
       </c>
       <c r="F46">
-        <v>-2.784938220763334</v>
+        <v>-2.674653526591622</v>
       </c>
       <c r="G46">
-        <v>-1.78762622041845</v>
+        <v>0.1119648100153569</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.856668918030577</v>
       </c>
       <c r="E47">
-        <v>-16.70853601232262</v>
+        <v>-15.82582321637748</v>
       </c>
       <c r="F47">
-        <v>-3.01911354369774</v>
+        <v>-2.908842931771875</v>
       </c>
       <c r="G47">
-        <v>-1.722113834741813</v>
+        <v>-0.04125716917873145</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.100141034753618</v>
       </c>
       <c r="E48">
-        <v>-16.70617214889062</v>
+        <v>-15.72187662400541</v>
       </c>
       <c r="F48">
-        <v>-3.249678013123343</v>
+        <v>-3.027797319181287</v>
       </c>
       <c r="G48">
-        <v>-2.011578005059067</v>
+        <v>0.223897665243655</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.357669956855987</v>
       </c>
       <c r="E49">
-        <v>-15.10570980815174</v>
+        <v>-15.03437275710891</v>
       </c>
       <c r="F49">
-        <v>-3.25934423234661</v>
+        <v>-3.006713712045234</v>
       </c>
       <c r="G49">
-        <v>-2.521368912651437</v>
+        <v>-0.36013884715795</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.620309118192494</v>
       </c>
       <c r="E50">
-        <v>-14.91264284730873</v>
+        <v>-14.22324154980301</v>
       </c>
       <c r="F50">
-        <v>-2.991736829402619</v>
+        <v>-3.480509216852648</v>
       </c>
       <c r="G50">
-        <v>-1.763588349257802</v>
+        <v>-0.07765661738301814</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.879033576085125</v>
       </c>
       <c r="E51">
-        <v>-15.07185946494441</v>
+        <v>-13.57621771206108</v>
       </c>
       <c r="F51">
-        <v>-2.858236310400048</v>
+        <v>-3.176007986522772</v>
       </c>
       <c r="G51">
-        <v>-2.687068337983039</v>
+        <v>-0.03680779597395097</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.133908877287377</v>
       </c>
       <c r="E52">
-        <v>-14.39881954402841</v>
+        <v>-13.23661838927787</v>
       </c>
       <c r="F52">
-        <v>-3.429254812171831</v>
+        <v>-3.249837059664681</v>
       </c>
       <c r="G52">
-        <v>-3.068211445919331</v>
+        <v>-0.2483615875699976</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.382646898697192</v>
       </c>
       <c r="E53">
-        <v>-14.3880100765721</v>
+        <v>-12.9288134825025</v>
       </c>
       <c r="F53">
-        <v>-3.712211034722295</v>
+        <v>-3.188398706133847</v>
       </c>
       <c r="G53">
-        <v>-1.423227851819792</v>
+        <v>0.06402480006117084</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.63419783360397</v>
       </c>
       <c r="E54">
-        <v>-13.38687315685237</v>
+        <v>-11.58288760878677</v>
       </c>
       <c r="F54">
-        <v>-3.433380910205175</v>
+        <v>-3.508030067075856</v>
       </c>
       <c r="G54">
-        <v>-2.06889016943493</v>
+        <v>-0.07967605016197357</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.897067098293599</v>
       </c>
       <c r="E55">
-        <v>-13.32405869389197</v>
+        <v>-11.02484375682155</v>
       </c>
       <c r="F55">
-        <v>-3.161017021634309</v>
+        <v>-3.459278988686299</v>
       </c>
       <c r="G55">
-        <v>-2.357857757921294</v>
+        <v>0.03482909895033825</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.182118939055959</v>
       </c>
       <c r="E56">
-        <v>-12.60820205123345</v>
+        <v>-10.37961772326066</v>
       </c>
       <c r="F56">
-        <v>-3.45078408097059</v>
+        <v>-3.703456848009509</v>
       </c>
       <c r="G56">
-        <v>-2.349905827535965</v>
+        <v>-0.3875965118606652</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.500162581428187</v>
       </c>
       <c r="E57">
-        <v>-12.03845662243241</v>
+        <v>-11.05068322950931</v>
       </c>
       <c r="F57">
-        <v>-3.473931151307017</v>
+        <v>-3.761070629241618</v>
       </c>
       <c r="G57">
-        <v>-2.452350659248712</v>
+        <v>-0.2039241347963605</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.849964491886503</v>
       </c>
       <c r="E58">
-        <v>-12.0891076042082</v>
+        <v>-9.427347566557698</v>
       </c>
       <c r="F58">
-        <v>-3.25233707248633</v>
+        <v>-3.814337138343835</v>
       </c>
       <c r="G58">
-        <v>-2.979968854570057</v>
+        <v>-0.2816391913307516</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.235703206060263</v>
       </c>
       <c r="E59">
-        <v>-11.32552990245685</v>
+        <v>-9.718741283529264</v>
       </c>
       <c r="F59">
-        <v>-3.823965252666573</v>
+        <v>-3.718779159859092</v>
       </c>
       <c r="G59">
-        <v>-2.702555070015749</v>
+        <v>-0.07564711624068053</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.64918605277991</v>
       </c>
       <c r="E60">
-        <v>-10.42464434031893</v>
+        <v>-9.332208856130553</v>
       </c>
       <c r="F60">
-        <v>-3.814675112244177</v>
+        <v>-3.566980833296082</v>
       </c>
       <c r="G60">
-        <v>-2.580915695266309</v>
+        <v>-0.2606370904296152</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.08746300011644</v>
       </c>
       <c r="E61">
-        <v>-10.14390612268741</v>
+        <v>-8.311563270385776</v>
       </c>
       <c r="F61">
-        <v>-3.892565670762012</v>
+        <v>-3.62433699226592</v>
       </c>
       <c r="G61">
-        <v>-3.119183915587489</v>
+        <v>-0.8341924156538876</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.547213463859155</v>
       </c>
       <c r="E62">
-        <v>-10.02006141552564</v>
+        <v>-8.253911267794125</v>
       </c>
       <c r="F62">
-        <v>-3.743596218879562</v>
+        <v>-3.713871082997505</v>
       </c>
       <c r="G62">
-        <v>-2.878470838881542</v>
+        <v>-0.6746539155708698</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.02095316106706</v>
       </c>
       <c r="E63">
-        <v>-10.23875501077807</v>
+        <v>-7.526058697489283</v>
       </c>
       <c r="F63">
-        <v>-3.59401626022125</v>
+        <v>-3.784755310022461</v>
       </c>
       <c r="G63">
-        <v>-3.319783111994087</v>
+        <v>-1.611998469014575</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.50663713243666</v>
       </c>
       <c r="E64">
-        <v>-10.4932914778012</v>
+        <v>-7.777144467318574</v>
       </c>
       <c r="F64">
-        <v>-3.709823679867426</v>
+        <v>-4.056766314079735</v>
       </c>
       <c r="G64">
-        <v>-2.229560876092379</v>
+        <v>-1.208850164878747</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.99075198441613</v>
       </c>
       <c r="E65">
-        <v>-10.06791380036469</v>
+        <v>-7.749969094798544</v>
       </c>
       <c r="F65">
-        <v>-3.767085404953345</v>
+        <v>-3.910387995433243</v>
       </c>
       <c r="G65">
-        <v>-3.681556217980104</v>
+        <v>-1.253813994393128</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.46745231397011</v>
       </c>
       <c r="E66">
-        <v>-9.350236711155087</v>
+        <v>-7.341921887389391</v>
       </c>
       <c r="F66">
-        <v>-3.925248078272063</v>
+        <v>-3.50954929289259</v>
       </c>
       <c r="G66">
-        <v>-3.701571776310537</v>
+        <v>-1.733790128858822</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.92484259581106</v>
       </c>
       <c r="E67">
-        <v>-8.961906479575331</v>
+        <v>-6.377216541061368</v>
       </c>
       <c r="F67">
-        <v>-3.793989121461467</v>
+        <v>-3.957632273517107</v>
       </c>
       <c r="G67">
-        <v>-3.548031984744679</v>
+        <v>-1.256445878096849</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.349811951645</v>
       </c>
       <c r="E68">
-        <v>-10.10563146037458</v>
+        <v>-6.842929336484195</v>
       </c>
       <c r="F68">
-        <v>-3.76409831209885</v>
+        <v>-3.893972238611965</v>
       </c>
       <c r="G68">
-        <v>-3.995707126383704</v>
+        <v>-1.699284312702999</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.73304980224097</v>
       </c>
       <c r="E69">
-        <v>-8.547143545212803</v>
+        <v>-5.999655020671852</v>
       </c>
       <c r="F69">
-        <v>-4.081506334931745</v>
+        <v>-3.951754178426842</v>
       </c>
       <c r="G69">
-        <v>-3.59694860563295</v>
+        <v>-1.494354922731034</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.058773408548</v>
       </c>
       <c r="E70">
-        <v>-9.630499439015798</v>
+        <v>-6.016256406383971</v>
       </c>
       <c r="F70">
-        <v>-4.198921615706755</v>
+        <v>-3.906609811709074</v>
       </c>
       <c r="G70">
-        <v>-3.994478913988634</v>
+        <v>-1.688164190236587</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.32325836341779</v>
       </c>
       <c r="E71">
-        <v>-8.863516324810677</v>
+        <v>-6.236666293285302</v>
       </c>
       <c r="F71">
-        <v>-3.903400716390629</v>
+        <v>-4.072964210274076</v>
       </c>
       <c r="G71">
-        <v>-3.650715175736253</v>
+        <v>-1.979766972972211</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.51910239239705</v>
       </c>
       <c r="E72">
-        <v>-8.512432791944009</v>
+        <v>-5.490405476139282</v>
       </c>
       <c r="F72">
-        <v>-4.084430471863628</v>
+        <v>-3.98237312273652</v>
       </c>
       <c r="G72">
-        <v>-3.454985791817923</v>
+        <v>-1.873859310625386</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-13.64185857508872</v>
       </c>
       <c r="E73">
-        <v>-9.534301065670856</v>
+        <v>-6.370949133034752</v>
       </c>
       <c r="F73">
-        <v>-4.197168790282432</v>
+        <v>-4.163132002068803</v>
       </c>
       <c r="G73">
-        <v>-3.840051896218251</v>
+        <v>-1.560479759332436</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-13.6920789499096</v>
       </c>
       <c r="E74">
-        <v>-9.454083677098984</v>
+        <v>-6.294508491785276</v>
       </c>
       <c r="F74">
-        <v>-4.212758664803118</v>
+        <v>-4.319830950186774</v>
       </c>
       <c r="G74">
-        <v>-3.472601204632385</v>
+        <v>-1.474177147669176</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-13.66644192219479</v>
       </c>
       <c r="E75">
-        <v>-9.140350997847582</v>
+        <v>-6.093557457694904</v>
       </c>
       <c r="F75">
-        <v>-3.875697625338805</v>
+        <v>-4.351502749465411</v>
       </c>
       <c r="G75">
-        <v>-3.340497195433307</v>
+        <v>-0.6244196975579689</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-13.56828441124201</v>
       </c>
       <c r="E76">
-        <v>-10.5265304770175</v>
+        <v>-6.457076180186634</v>
       </c>
       <c r="F76">
-        <v>-4.132551991027056</v>
+        <v>-4.527711406654116</v>
       </c>
       <c r="G76">
-        <v>-2.752140421102954</v>
+        <v>-0.6972881154228669</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-13.39977469305925</v>
       </c>
       <c r="E77">
-        <v>-9.422819092550029</v>
+        <v>-7.955172365982119</v>
       </c>
       <c r="F77">
-        <v>-4.122984347524722</v>
+        <v>-4.78671787085484</v>
       </c>
       <c r="G77">
-        <v>-1.744734792411653</v>
+        <v>-0.5805086215250759</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-13.1640088204383</v>
       </c>
       <c r="E78">
-        <v>-9.790345514538547</v>
+        <v>-8.391056103116421</v>
       </c>
       <c r="F78">
-        <v>-4.322258066676977</v>
+        <v>-4.594108367458107</v>
       </c>
       <c r="G78">
-        <v>-2.495235466164431</v>
+        <v>-0.5518558498826837</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.87266059242054</v>
       </c>
       <c r="E79">
-        <v>-12.20144545891648</v>
+        <v>-8.013526282044959</v>
       </c>
       <c r="F79">
-        <v>-4.621939855457365</v>
+        <v>-4.428486245677179</v>
       </c>
       <c r="G79">
-        <v>-2.031821991031711</v>
+        <v>0.3861508126688751</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.53436756494148</v>
       </c>
       <c r="E80">
-        <v>-11.40095616552861</v>
+        <v>-8.439995321717316</v>
       </c>
       <c r="F80">
-        <v>-4.638459986571395</v>
+        <v>-5.000980069793349</v>
       </c>
       <c r="G80">
-        <v>-2.764793326154048</v>
+        <v>-0.1281755423122965</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.1652229930986</v>
       </c>
       <c r="E81">
-        <v>-10.52986796236115</v>
+        <v>-9.024603202211528</v>
       </c>
       <c r="F81">
-        <v>-5.009484089550488</v>
+        <v>-4.955753694702704</v>
       </c>
       <c r="G81">
-        <v>-2.289938605637607</v>
+        <v>0.5606695313170951</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.77595955628342</v>
       </c>
       <c r="E82">
-        <v>-12.70059650641195</v>
+        <v>-9.753397695109964</v>
       </c>
       <c r="F82">
-        <v>-4.909977283656601</v>
+        <v>-4.86118644363171</v>
       </c>
       <c r="G82">
-        <v>-2.690574205709127</v>
+        <v>0.733907068841617</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.37985432093872</v>
       </c>
       <c r="E83">
-        <v>-13.32784902663639</v>
+        <v>-11.31219354650426</v>
       </c>
       <c r="F83">
-        <v>-4.92030702516951</v>
+        <v>-5.274114340048818</v>
       </c>
       <c r="G83">
-        <v>-1.695367937330041</v>
+        <v>0.8636605907078119</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.99354420378083</v>
       </c>
       <c r="E84">
-        <v>-13.83369315871519</v>
+        <v>-12.15125185301546</v>
       </c>
       <c r="F84">
-        <v>-5.062090389832674</v>
+        <v>-5.334188372467241</v>
       </c>
       <c r="G84">
-        <v>-1.599186657777595</v>
+        <v>0.8561092363327343</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.6286739437444</v>
       </c>
       <c r="E85">
-        <v>-15.32062665608177</v>
+        <v>-13.06643833606961</v>
       </c>
       <c r="F85">
-        <v>-5.26687440894835</v>
+        <v>-5.485478909812334</v>
       </c>
       <c r="G85">
-        <v>-0.9737484628618646</v>
+        <v>0.9702038777981765</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.30524564618619</v>
       </c>
       <c r="E86">
-        <v>-16.11245750716698</v>
+        <v>-14.68559874598616</v>
       </c>
       <c r="F86">
-        <v>-5.074358511068135</v>
+        <v>-5.518332789374766</v>
       </c>
       <c r="G86">
-        <v>-1.240260620955352</v>
+        <v>1.543865140479706</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.03218965624394</v>
       </c>
       <c r="E87">
-        <v>-17.39548740539018</v>
+        <v>-15.50820510642749</v>
       </c>
       <c r="F87">
-        <v>-5.089752062514358</v>
+        <v>-5.541213953774894</v>
       </c>
       <c r="G87">
-        <v>-0.8220890611623122</v>
+        <v>1.235560655498459</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.817820486144374</v>
       </c>
       <c r="E88">
-        <v>-18.94063443612536</v>
+        <v>-16.85382757238472</v>
       </c>
       <c r="F88">
-        <v>-5.472629274660108</v>
+        <v>-5.777854498100031</v>
       </c>
       <c r="G88">
-        <v>-0.8635635756783016</v>
+        <v>1.503936650730556</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.666200077200937</v>
       </c>
       <c r="E89">
-        <v>-21.29646888371369</v>
+        <v>-18.79839053907043</v>
       </c>
       <c r="F89">
-        <v>-5.866975233497619</v>
+        <v>-6.021303394108778</v>
       </c>
       <c r="G89">
-        <v>-1.173546507247959</v>
+        <v>1.483649627665902</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.574917550616997</v>
       </c>
       <c r="E90">
-        <v>-21.95185681294779</v>
+        <v>-19.88382953091695</v>
       </c>
       <c r="F90">
-        <v>-5.645340564674195</v>
+        <v>-5.934302450894954</v>
       </c>
       <c r="G90">
-        <v>-1.846057349186587</v>
+        <v>1.849984665405034</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.544215923032223</v>
       </c>
       <c r="E91">
-        <v>-24.97820882142985</v>
+        <v>-21.65468929161645</v>
       </c>
       <c r="F91">
-        <v>-5.291816551446644</v>
+        <v>-5.896310208332958</v>
       </c>
       <c r="G91">
-        <v>-0.9945982786681945</v>
+        <v>1.33734999919443</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.561474469488877</v>
       </c>
       <c r="E92">
-        <v>-26.32008623938273</v>
+        <v>-24.24367222348968</v>
       </c>
       <c r="F92">
-        <v>-5.572882439583919</v>
+        <v>-6.032529429151517</v>
       </c>
       <c r="G92">
-        <v>-1.55342167624271</v>
+        <v>1.406004092587836</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.618234981886086</v>
       </c>
       <c r="E93">
-        <v>-27.94871568844931</v>
+        <v>-26.42574006645568</v>
       </c>
       <c r="F93">
-        <v>-5.491119263457996</v>
+        <v>-6.004031105393006</v>
       </c>
       <c r="G93">
-        <v>-1.871816704027656</v>
+        <v>0.8062060728737604</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.699807548677462</v>
       </c>
       <c r="E94">
-        <v>-30.62293355809491</v>
+        <v>-28.11646395111544</v>
       </c>
       <c r="F94">
-        <v>-5.791631904743393</v>
+        <v>-6.128504076439868</v>
       </c>
       <c r="G94">
-        <v>-2.083257937075367</v>
+        <v>0.9660094165999199</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.797094542250498</v>
       </c>
       <c r="E95">
-        <v>-32.69831508191421</v>
+        <v>-30.78506651299153</v>
       </c>
       <c r="F95">
-        <v>-5.672899519797931</v>
+        <v>-6.210296245424888</v>
       </c>
       <c r="G95">
-        <v>-2.444094158673769</v>
+        <v>0.6763830295512409</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.899286196888726</v>
       </c>
       <c r="E96">
-        <v>-34.18052990936479</v>
+        <v>-32.88964763721228</v>
       </c>
       <c r="F96">
-        <v>-5.855720205595782</v>
+        <v>-6.235189100062715</v>
       </c>
       <c r="G96">
-        <v>-3.20825745386712</v>
+        <v>0.06267078693560893</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.992873153879884</v>
       </c>
       <c r="E97">
-        <v>-36.78722370308203</v>
+        <v>-35.79205078363039</v>
       </c>
       <c r="F97">
-        <v>-6.107559635027485</v>
+        <v>-6.434111177252481</v>
       </c>
       <c r="G97">
-        <v>-3.415762448268638</v>
+        <v>-0.4507716523865773</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.06445051046984</v>
       </c>
       <c r="E98">
-        <v>-39.30430578889847</v>
+        <v>-38.13466887982734</v>
       </c>
       <c r="F98">
-        <v>-5.905993823271684</v>
+        <v>-6.359028784230136</v>
       </c>
       <c r="G98">
-        <v>-3.744433409407481</v>
+        <v>-1.191340689521542</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.1032891793319</v>
       </c>
       <c r="E99">
-        <v>-42.33684595711201</v>
+        <v>-41.11049443956881</v>
       </c>
       <c r="F99">
-        <v>-6.324269659641266</v>
+        <v>-6.743939638349761</v>
       </c>
       <c r="G99">
-        <v>-3.898976296271739</v>
+        <v>-1.509775443852959</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.0966865587044</v>
       </c>
       <c r="E100">
-        <v>-44.52892399187197</v>
+        <v>-43.32454236597698</v>
       </c>
       <c r="F100">
-        <v>-5.858614521301163</v>
+        <v>-6.563904337943823</v>
       </c>
       <c r="G100">
-        <v>-4.711450382519674</v>
+        <v>-2.483939884784438</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.05141350644992</v>
       </c>
       <c r="E101">
-        <v>-47.2274258033837</v>
+        <v>-46.12212945301355</v>
       </c>
       <c r="F101">
-        <v>-6.311948108708325</v>
+        <v>-6.742432423860366</v>
       </c>
       <c r="G101">
-        <v>-5.573082759480246</v>
+        <v>-3.001841628948022</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.949659624659827</v>
       </c>
       <c r="E102">
-        <v>-49.55333383049234</v>
+        <v>-48.33229874143414</v>
       </c>
       <c r="F102">
-        <v>-6.050109042173728</v>
+        <v>-6.53662164334892</v>
       </c>
       <c r="G102">
-        <v>-6.169182899826955</v>
+        <v>-3.075368845375235</v>
       </c>
     </row>
   </sheetData>
